--- a/docs/Test_Report/Cdd_Uart/TestPlanExecutionReport_Cdd_Uart.xlsx
+++ b/docs/Test_Report/Cdd_Uart/TestPlanExecutionReport_Cdd_Uart.xlsx
@@ -43,7 +43,7 @@
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000000FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
@@ -104,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -136,13 +131,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -734,7 +726,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09 06:51:21.839842-05:00 CDT</t>
+          <t>2025-06-10 02:10:58.413311-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -806,12 +798,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1028,12 +1020,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1119,12 +1111,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -6226,9 +6218,9 @@
       </c>
       <c r="S52" s="3" t="inlineStr"/>
       <c r="T52" s="3" t="inlineStr"/>
-      <c r="U52" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U52" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6317,9 +6309,9 @@
       </c>
       <c r="S53" s="3" t="inlineStr"/>
       <c r="T53" s="3" t="inlineStr"/>
-      <c r="U53" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U53" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6408,9 +6400,9 @@
       </c>
       <c r="S54" s="3" t="inlineStr"/>
       <c r="T54" s="3" t="inlineStr"/>
-      <c r="U54" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U54" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6503,9 +6495,9 @@
       </c>
       <c r="S55" s="3" t="inlineStr"/>
       <c r="T55" s="3" t="inlineStr"/>
-      <c r="U55" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U55" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6594,9 +6586,9 @@
       </c>
       <c r="S56" s="3" t="inlineStr"/>
       <c r="T56" s="3" t="inlineStr"/>
-      <c r="U56" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U56" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6685,9 +6677,9 @@
       </c>
       <c r="S57" s="3" t="inlineStr"/>
       <c r="T57" s="3" t="inlineStr"/>
-      <c r="U57" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U57" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6780,9 +6772,9 @@
       </c>
       <c r="S58" s="3" t="inlineStr"/>
       <c r="T58" s="3" t="inlineStr"/>
-      <c r="U58" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U58" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6871,9 +6863,9 @@
       </c>
       <c r="S59" s="3" t="inlineStr"/>
       <c r="T59" s="3" t="inlineStr"/>
-      <c r="U59" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U59" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6927,12 +6919,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Test Plan</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Test Plan Key</t>
         </is>
@@ -6954,8 +6946,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n"/>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Test Plan Name</t>
         </is>
@@ -6977,8 +6969,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Test Case Key</t>
         </is>
@@ -7000,8 +6992,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
@@ -7023,8 +7015,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Associated Issue(s) Type</t>
         </is>
@@ -7051,8 +7043,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Associated Issue(s) ID(s)</t>
         </is>
@@ -7074,8 +7066,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Test Platform</t>
         </is>
@@ -7097,8 +7089,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Test Level</t>
         </is>
@@ -7114,7 +7106,7 @@
 -- "Not Provided" if no 'Test Scope' is provided in Jira</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7126,8 +7118,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Test Description</t>
         </is>
@@ -7149,8 +7141,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Test Setup</t>
         </is>
@@ -7172,8 +7164,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Pass/Fail Criteria</t>
         </is>
@@ -7195,8 +7187,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
@@ -7207,7 +7199,7 @@
 (Map Test Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7219,15 +7211,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="13" t="n"/>
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Functional:
 Tests covering functional requirements-based  aspects of the software</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7239,8 +7231,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="13" t="n"/>
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="12" t="n"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Compatability:
@@ -7248,7 +7240,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing that measures the degree to which a test item can function satisfactorily alongside other independent products in a shared environment (co-existence), and where necessary, exchanges information with other systems or components (interoperability)</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7260,15 +7252,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="13" t="n"/>
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Usability:
 Test Case covers usability/api/look and feel aspects of the module including out-of box (OOB) experience</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7280,15 +7272,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="13" t="n"/>
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="12" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Fault Injection:
 Testing based on injection of errors or faults to ensure no unintended consequences</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7300,8 +7292,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="13" t="n"/>
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="12" t="n"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Performance: 
@@ -7309,7 +7301,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item accomplishes its designated functions within given constraints of time and other resources</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7321,8 +7313,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="13" t="n"/>
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="12" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Reliability: 
@@ -7330,7 +7322,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ability of a test item to perform its required functions, including evaluating the frequency with which failures occur, when it is used under stated conditions for a specified period of time</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7342,8 +7334,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="13" t="n"/>
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="12" t="n"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Stress:
@@ -7351,7 +7343,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of performance efficiency testing conducted to evaluate a test item's behaviour under conditions of loading above anticipated or specified capacity requirements, or of resource availability below minimum specified requirements</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7363,8 +7355,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="13" t="n"/>
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="12" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Security:
@@ -7372,7 +7364,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item, and associated data and information, are protected so that unauthorized persons or systems cannot use, read, or modify them, and authorized persons or systems are not denied access to them</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7384,8 +7376,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="13" t="n"/>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="n"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Maintainability:
@@ -7393,7 +7385,7 @@
 ISO/IEC/IEEE 29119-1 Defn: test type conducted to evaluate the degree of effectiveness and efficiency with which a test item may be modified</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7405,8 +7397,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="13" t="n"/>
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="12" t="n"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Portability:
@@ -7414,7 +7406,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ease with which a test item can be transferred from one hardware or software environment to another, including the level of modification needed for it to be executed in various types of environment</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7426,8 +7418,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Test Design Technique</t>
         </is>
@@ -7439,7 +7431,7 @@
 (Map Test Derivation Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7451,8 +7443,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="13" t="n"/>
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="12" t="n"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Requirements-Analysis:
@@ -7460,7 +7452,7 @@
 </t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7472,15 +7464,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="13" t="n"/>
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="12" t="n"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Boundary Value Analysis:
 Test cases that apply to interfaces and values approaching and crossing the boundaries and out of range values</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7492,15 +7484,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="13" t="n"/>
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="12" t="n"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Error Guessing:
 Test cases established based on lessons learned and expert judgement to determine situations that may cause software failures or errors to appear</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7512,28 +7504,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="13" t="n"/>
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="12" t="n"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Other (Use case analysis; Customer Usage; Requirement analysis; Failure Mode analysis):
 Teams are encouraged to use techniques defined by standards such as ISO/IEC/IEEE 29119-4; which needs to be refelcted within Qmetry</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Test Execution Type</t>
         </is>
@@ -7543,7 +7535,7 @@
           <t>Identifies whether the case is automated or manually or Semi-Automated executed</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7555,8 +7547,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Test Category</t>
         </is>
@@ -7566,7 +7558,7 @@
           <t>Test Categories represent sets of tests that are commonly used.</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7578,15 +7570,15 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="13" t="n"/>
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="12" t="n"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Sanity:
 This Test case is identified to run for Sanity Checks. These are mainly the basic tests that need to be run as part of entry to validate phase</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7598,15 +7590,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="13" t="n"/>
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="12" t="n"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Full:
 This category means running all test cases for identified releases</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7618,15 +7610,15 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="13" t="n"/>
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="12" t="n"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Base Regression:
 This Test case is identified to run for the Base Regression / maintenance releases</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -7638,8 +7630,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Test Component(s)</t>
         </is>
@@ -7649,24 +7641,24 @@
           <t xml:space="preserve">The field provides the Component(s) (in Jira) to which the Test Case is mapped to. </t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Test Execution</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Build/Release Key</t>
         </is>
@@ -7688,8 +7680,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n"/>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Defect Key</t>
         </is>
@@ -7711,8 +7703,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="n"/>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Defect Summary</t>
         </is>
@@ -7734,8 +7726,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
@@ -7758,8 +7750,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n"/>
-      <c r="B39" s="13" t="n"/>
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="12" t="n"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
           <t>PASS
@@ -7778,8 +7770,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="13" t="n"/>
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="12" t="n"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
           <t>FAIL
@@ -7798,8 +7790,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n"/>
-      <c r="B41" s="13" t="n"/>
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="12" t="n"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
           <t>BLOCKED
@@ -7818,8 +7810,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="n"/>
-      <c r="B42" s="13" t="n"/>
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="12" t="n"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
           <t>WIP

--- a/docs/Test_Report/Cdd_Uart/TestPlanExecutionReport_Cdd_Uart.xlsx
+++ b/docs/Test_Report/Cdd_Uart/TestPlanExecutionReport_Cdd_Uart.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283,MCAL-32347</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10 02:10:58.413311-05:00 CDT</t>
+          <t>2025-08-29 05:08:36.477731-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="inlineStr">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="7" t="inlineStr">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1388,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U59"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1524,12 +1524,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1543,7 +1543,11 @@
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -1561,7 +1565,40 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t xml:space="preserve">
+{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test8",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test8/Cdd_Uart_Test8.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -1581,7 +1618,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -1596,12 +1633,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1615,22 +1652,22 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30004</t>
+          <t>MCAL-30000</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>CDD UART: Cdd_Uart shall verify Configurator support of CDD UART module</t>
+          <t>CDD UART supports Software Test of Basic Tx RX functionality at 57600 baudrate</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -1642,22 +1679,54 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart shall verify Configurator support of CDD UART module by means of a compatible plugin per hardware SoC.</t>
+          <t>Verify that CDD UART shall be able to transmitted and receive data at 57600 baudrate</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test7",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test7/Cdd_Uart_Test7.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>UART shall be bundled with a compatible loadable plugin across configurator tools such as EB Tresos, DaVinci Configurator.</t>
+          <t>UART Driver should be able Receive the transmitted data at 57600 baudrate</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -1672,7 +1741,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1687,12 +1756,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1706,22 +1775,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30003</t>
+          <t>MCAL-29999</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>CDD UART: MCAL Module State Machine</t>
+          <t>CDD UART supports Software Test of Basic Tx RX functionality at 9600 baudrate</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -1733,22 +1802,54 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>CDD UART shall maintain distinct states: Initialized, Un Initialized</t>
+          <t>Verify that CDD UART shall be able to transmitted and receive data at 9600 baudrate</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test6",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test6/Cdd_Uart_Test6.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>UART must keep a track on internal states, checkable by inspecting UART Driver Status global variable within UART source</t>
+          <t>UART Driver should be able Receive the transmitted data at 9600 baudrate</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -1763,7 +1864,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1778,12 +1879,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1797,26 +1898,30 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30002</t>
+          <t>MCAL-29948</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>AUTOSAR Configurator (Manual Integration Test Case)</t>
+          <t>GetVersionInfo API Positive Test</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -1829,17 +1934,49 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>The MCAL shall support EB Tresos Configurator for configuration of MCAL modules. The ASIL level is applicable for generated configuration header and source files only.</t>
+          <t>Valid versioninfo pointer is passed as argument to Cdd_Uart_GetVersionInfo and CDD_UART_GET_VERSION_INFO_API ON, CDD_UART_DEV_ERROR_DETECT is OFF</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test5",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test5/Cdd_Uart_Test5.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>The MCAL shall support EB Tresos Configurator for configuration of MCAL modules.</t>
+          <t>Cdd_Uart_GetVersionInfo should return the vendor ID, module ID, software major version, software minor version and software patch version</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -1854,7 +1991,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1869,12 +2006,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -1888,26 +2025,30 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30000</t>
+          <t>MCAL-29951</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>CDD UART supports Software Test of Basic Tx RX functionality at 57600 baudrate</t>
+          <t>UART Init Positive Test</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -1915,22 +2056,54 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Verify that CDD UART shall be able to transmitted and receive data at 57600 baudrate</t>
+          <t>Null pointer is passed as argument to Cdd_Uart_init and CDD_UART_DEV_ERROR_DETECT is OFF</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test5",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test5/Cdd_Uart_Test5.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>UART Driver should be able Receive the transmitted data at 57600 baudrate</t>
+          <t>Uart Driver should return Cdd_Uart_IsInitialized  as TRUE</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1945,7 +2118,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1960,12 +2133,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -1979,26 +2152,30 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29999</t>
+          <t>MCAL-29997</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>CDD UART supports Software Test of Basic Tx RX functionality at 9600 baudrate</t>
+          <t>CDD UART supports Software Test of Basic Functionality using Digital I/O Loopback</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -2011,17 +2188,49 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Verify that CDD UART shall be able to transmitted and receive data at 9600 baudrate</t>
+          <t>Verify that CDD UART shall be able to read the transmitted data with a specified configuration on an IO loopback.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test4",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test4/Cdd_Uart_Test4.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>UART Driver should be able Receive the transmitted data at 9600 baudrate</t>
+          <t>UART Driver should be able Receive the transmitted data in Loopback mode</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -2036,7 +2245,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -2051,12 +2260,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2070,22 +2279,22 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29998</t>
+          <t>MCAL-29966</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>CDD UART supports Software Test of Basic Tx RX functionality at 115200 baudrate</t>
+          <t>UART Write Positive Test ISR mode</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
@@ -2097,22 +2306,55 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Verify that CDD UART shall be able to transmitted and receive data at 115200 baudrate</t>
+          <t>CDD Uart is initialized 
+Transmit 20 byte data to remote device  using Cdd_Uart_Write.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test3",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test3/Cdd_Uart_Test3.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>UART Driver should be able Receive the transmitted data at 115200 baudrate</t>
+          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -2127,7 +2369,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -2142,12 +2384,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2161,30 +2403,26 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29997</t>
+          <t>MCAL-29957</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>CDD UART supports Software Test of Basic Functionality using Digital I/O Loopback</t>
+          <t>UART Read Positive Test Interrupt Mode</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -2192,22 +2430,54 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Verify that CDD UART shall be able to read the transmitted data with a specified configuration on an IO loopback.</t>
+          <t>CDD Uart is initialized in ISR mode and 10 byte data is sent by the remote device  Cdd_Uart_Read is called with valid inputs</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test3",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test3/Cdd_Uart_Test3.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>UART Driver should be able Receive the transmitted data in Loopback mode</t>
+          <t>Uart Driver should return E_OK &amp; data should be received in the Destination buffer</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -2222,7 +2492,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2237,12 +2507,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2256,26 +2526,30 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29996</t>
+          <t>MCAL-29962</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_GetReadStatus Negative Test</t>
+          <t>UART Read Negative Test</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -2288,18 +2562,50 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is uninitialized.
-call Cdd_Uart_GetReadStatus</t>
+          <t>CDD Uart is initialized and Read enable is FALSE.
+Cdd_Uart_Read is called with valid inputs</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test2/Cdd_Uart_Test2.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
+          <t>Uart Driver should return CDD_UART_E_PARAM_VALUE</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -2314,7 +2620,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2329,12 +2635,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2348,26 +2654,30 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29995</t>
+          <t>MCAL-29971</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_GetReadStatus Negative Test</t>
+          <t>UART Write Negative Test</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -2380,18 +2690,50 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized.
-call Cdd_Uart_GetReadStatus with ReadStatus as NULL Pointer</t>
+          <t>CDD Uart is initialized and Write enable is FALSE.
+Cdd_Uart_Write is called with valid inputs</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test2/Cdd_Uart_Test2.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_POINTER</t>
+          <t>Uart Driver should return CDD_UART_E_PARAM_VALUE</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -2406,7 +2748,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2421,12 +2763,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2440,22 +2782,22 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29994</t>
+          <t>MCAL-29947</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_GetReadStatus Negative Test</t>
+          <t>GetVersionInfo API Positive Test</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
@@ -2472,18 +2814,49 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized.
-call Cdd_Uart_GetReadStatus with invalid HwUnitId</t>
+          <t>Valid versioninfo pointer is passed as argument to Cdd_Uart_GetVersionInfo and CDD_UART_GET_VERSION_INFO_API ON, CDD_UART_DEV_ERROR_DETECT is ON</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
+          <t>Cdd_Uart_GetVersionInfo should return the vendor ID, module ID, software major version, software minor version and software patch version</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -2498,7 +2871,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2513,12 +2886,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2532,22 +2905,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29993</t>
+          <t>MCAL-29949</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_GetReadStatus Positive Test</t>
+          <t>GetVersionInfo API Negative Test</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
@@ -2564,18 +2937,49 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized.
-call Cdd_Uart_GetReadStatus with valid inputs</t>
+          <t>Null pointer is passed as argument to Cdd_Uart_GetVersionInfo and CDD_UART_GET_VERSION_INFO_API ON, CDD_UART_DEV_ERROR_DETECT is ON</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return E_OK and ReadStatus is updated with the status of write operation</t>
+          <t>Cdd_Uart_GetVersionInfo should return CDD_UART_E_PARAM_POINTER</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -2590,7 +2994,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2605,12 +3009,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -2624,22 +3028,22 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29992</t>
+          <t>MCAL-29952</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_GetWriteStatus Negative Test</t>
+          <t>UART Init Negative Test</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
@@ -2656,18 +3060,49 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is uninitialized.
-call Cdd_Uart_GetWriteStatus</t>
+          <t>Not NULL pointer is passed as argument to Cdd_Uart_init and CDD_UART_DEV_ERROR_DETECT is ON</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
+          <t>Uart Driver should return CDD_UART_E_PARAM_POINTER</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -2682,7 +3117,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2697,12 +3132,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -2716,22 +3151,22 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29991</t>
+          <t>MCAL-29955</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_GetWriteStatus Negative Test</t>
+          <t>UART Deinit Negative Test</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
@@ -2748,18 +3183,49 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized.
-call Cdd_Uart_GetWriteStatus with WriteStatus as NULL Pointer</t>
+          <t>CDD Uart is uninitialized and Cdd_Uart_Deinit is called</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_POINTER</t>
+          <t>Uart Driver should return CDD_UART_E_NOT_INITIALIZED</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2774,7 +3240,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -2789,12 +3255,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -2808,22 +3274,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29990</t>
+          <t>MCAL-29958</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_GetWriteStatus Negative Test</t>
+          <t>UART Read Negative Test</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
@@ -2840,18 +3306,49 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized.
-call Cdd_Uart_GetWriteStatus with invalid HwUnitId</t>
+          <t>CDD Uart is uninitialized and  Cdd_Uart_Read is called with valid inputs</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
+          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -2866,7 +3363,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2881,12 +3378,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -2900,22 +3397,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29989</t>
+          <t>MCAL-29967</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_GetWriteStatus Positive Test</t>
+          <t>UART Write Negative Test</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
@@ -2932,18 +3429,49 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized.
-call Cdd_Uart_GetWriteStatus with valid inputs</t>
+          <t>CDD Uart is uninitialized and  Cdd_Uart_Write is called with valid inputs</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return E_OK and WriteStatus is updated with the status of write operation</t>
+          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2958,7 +3486,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2973,12 +3501,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -2992,22 +3520,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29988</t>
+          <t>MCAL-29980</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_Poll_Read Negative Test</t>
+          <t>Cdd_Uart_MainFunction_Write Negative Test</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr"/>
@@ -3025,12 +3553,44 @@
       <c r="I18" s="3" t="inlineStr">
         <is>
           <t>CDD Uart is uninitialized.
-call Cdd_Uart_Poll_Read</t>
+call Cdd_Uart_MainFunction_Write</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -3050,7 +3610,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -3065,12 +3625,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3084,30 +3644,26 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29987</t>
+          <t>MCAL-29988</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_Poll_Read positive Test</t>
+          <t>Cdd_Uart_Poll_Read Negative Test</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -3120,18 +3676,50 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized.
+          <t>CDD Uart is uninitialized.
 call Cdd_Uart_Poll_Read</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>CC UART should return Cdd_Uart_ReadDone as TRUE;</t>
+          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3146,7 +3734,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3161,12 +3749,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3180,12 +3768,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -3218,7 +3806,39 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -3238,7 +3858,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -3253,12 +3873,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -3272,22 +3892,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29985</t>
+          <t>MCAL-29983</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_CancelRead Negative Test</t>
+          <t>Cdd_Uart_CancelWrite Negative Test</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
@@ -3304,18 +3924,50 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized.
-call Cdd_Uart_CancelRead with invalid HwUnitId</t>
+          <t>CDD Uart is uninitialized.
+call Cdd_Uart_CancelWrite</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
+          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3330,7 +3982,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3345,12 +3997,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -3364,22 +4016,22 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29984</t>
+          <t>MCAL-29992</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Uart_CancelRead Positive Test</t>
+          <t>Cdd_Uart_GetWriteStatus Negative Test</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr"/>
@@ -3396,1900 +4048,2578 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
+          <t>CDD Uart is uninitialized.
+call Cdd_Uart_GetWriteStatus</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29996</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Cdd_Uart_GetReadStatus Negative Test</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is uninitialized.
+call Cdd_Uart_GetReadStatus</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29950</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>UART Init Positive Test</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Null pointer is passed as argument to Cdd_Uart_init and CDD_UART_DEV_ERROR_DETECT is ON</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return Cdd_Uart_IsInitialized  as TRUE</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29953</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>UART Init Negative Test</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>NULL pointer is passed as argument to Cdd_Uart_init and CDD_UART_DEV_ERROR_DETECT is ON &amp; CDD UART is already initialized</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return CDD_UART_E_ALREADY_INITIALIZED</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29956</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>UART Read Positive Test Polling Mode</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized in Polling mode and 10 byte data is sent by the remote device  Cdd_Uart_Read is called with valid inputs</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return E_OK &amp; data should be received in the Destination buffer</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29963</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>UART Write Positive Test Polling mode</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized 
+Transmit 20 byte data to remote device  using Cdd_Uart_Write.</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29964</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>UART Write Positive Test Polling mode Large data</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized 
+Transmit 100 byte data to remote device  using Cdd_Uart_Write.</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29979</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Cdd_Uart_MainFunction_Write Positive Test</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized.
+Transmit 12 byte data to remote device  using Cdd_Uart_Write and Cdd_Uart_MainFunction_Write</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29987</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Cdd_Uart_Poll_Read positive Test</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized.
+call Cdd_Uart_Poll_Read</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>CC UART should return Cdd_Uart_ReadDone as TRUE;</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29959</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>UART Read Negative Test</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized and  Cdd_Uart_Read is called with  HW unit ID greater than CDD_UART_MAX_NUM_HWUNIT</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29960</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>UART Read Negative Test</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized and  Cdd_Uart_Read is called with invalid inputs : Destination buffer  as NULL PTR</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return E_NOT_OK</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29961</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>UART Read Negative Test</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized and  Cdd_Uart_Read is called with invalid inputs : Data count = 0</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return E_NOT_OK</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29968</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>UART Write Negative Test</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized and  Cdd_Uart_Write is called with  HW unit ID greater than CDD_UART_MAX_NUM_HWUNIT</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29969</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>UART Write Negative Test</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized and  Cdd_Uart_Write is called with invalid inputs : Source buffer  as NULL PTR</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return E_NOT_OK</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29970</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>UART Write Negative Test</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>CDD Uart is initialized and  Cdd_Uart_Write is called with invalid inputs : Data count = 0</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Uart Driver should return E_NOT_OK</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29976</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>UART Read callback function</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>CddUartReadDoneCallback should be called after a successful Reception</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>CC UART should return Cdd_Uart_ReadDone as TRUE;</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29977</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>UART Write callback function</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>CddUartWriteDoneCallback should be called after a successful Transmission</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>CC UART should return Cdd_Uart_WriteDone as TRUE;</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29974</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Overrun error Test Case</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Verify that CDD UART shall detect break error while attempting to read data serially.</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Cdd_Uart_Error callback function should be called</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29978</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>UART Error callback</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>CddUartErrorCallback should be called after an error occurs</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>CC UART should return Cdd_Uart_Error as TRUE;</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>CDD UART</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29984</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Cdd_Uart_CancelRead Positive Test</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
           <t>CDD Uart is initialized.
 Inittiate UART Read.
 call Cdd_Uart_CancelRead valid HwUnitId</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>Uart Driver should return E_OK</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M41" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr">
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t>CDD UART</t>
         </is>
       </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr"/>
-      <c r="T22" s="3" t="inlineStr"/>
-      <c r="U22" s="10" t="inlineStr">
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32283</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29983</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Cdd_Uart_CancelWrite Negative Test</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32284</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29981</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Cdd_Uart_CancelWrite Positive Test</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is uninitialized.
-call Cdd_Uart_CancelWrite</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr"/>
-      <c r="U23" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29982</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Cdd_Uart_CancelWrite Negative Test</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is initialized.
-call Cdd_Uart_CancelWrite with invalid HwUnitId</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr"/>
-      <c r="T24" s="3" t="inlineStr"/>
-      <c r="U24" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29981</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Cdd_Uart_CancelWrite Positive Test</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>CDD Uart is initialized.
 Inittiate UART Write.
 call Cdd_Uart_CancelWrite valid HwUnitId</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>Uart Driver should return E_OK</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr">
+      <c r="P42" s="3" t="inlineStr">
         <is>
           <t>CDD UART</t>
         </is>
       </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr"/>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29980</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Cdd_Uart_MainFunction_Write Negative Test</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is uninitialized.
-call Cdd_Uart_MainFunction_Write</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr"/>
-      <c r="T26" s="3" t="inlineStr"/>
-      <c r="U26" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29979</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Cdd_Uart_MainFunction_Write Positive Test</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is initialized.
-Transmit 12 byte data to remote device  using Cdd_Uart_Write and Cdd_Uart_MainFunction_Write</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr"/>
-      <c r="T27" s="3" t="inlineStr"/>
-      <c r="U27" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29978</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>UART Error callback</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>CddUartErrorCallback should be called after an error occurs</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>CC UART should return Cdd_Uart_Error as TRUE;</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr"/>
-      <c r="T28" s="3" t="inlineStr"/>
-      <c r="U28" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29977</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>UART Write callback function</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>CddUartWriteDoneCallback should be called after a successful Transmission</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>CC UART should return Cdd_Uart_WriteDone as TRUE;</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr"/>
-      <c r="T29" s="3" t="inlineStr"/>
-      <c r="U29" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29976</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>UART Read callback function</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>CddUartReadDoneCallback should be called after a successful Reception</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>CC UART should return Cdd_Uart_ReadDone as TRUE;</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr"/>
-      <c r="T30" s="3" t="inlineStr"/>
-      <c r="U30" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29975</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Break error Test Case</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>Verify that CDD UART shall detect overrun error while attempting to read data serially.</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>CDD Driver should provides a method to detect Break error</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr"/>
-      <c r="T31" s="3" t="inlineStr"/>
-      <c r="U31" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29974</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Overrun error Test Case</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>Verify that CDD UART shall detect break error while attempting to read data serially.</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>Cdd_Uart_Error callback function should be called</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29973</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Framing error Test Case</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>Verify that CDD UART shall detect framing error while attempting to read data serially.</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>CDD Driver should provides a method to detect Framing error</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr"/>
-      <c r="T33" s="3" t="inlineStr"/>
-      <c r="U33" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29972</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Parity error Test Case</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>Verify that CDD UART shall detect parity error while attempting to read data serially.</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>CDD Driver should provides a method to detect parity error</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29971</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>UART Write Negative Test</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is initialized and Write enable is FALSE.
-Cdd_Uart_Write is called with valid inputs</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_VALUE</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr"/>
-      <c r="U35" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29970</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>UART Write Negative Test</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is initialized and  Cdd_Uart_Write is called with invalid inputs : Data count = 0</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return E_NOT_OK</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr"/>
-      <c r="T36" s="3" t="inlineStr"/>
-      <c r="U36" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29969</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>UART Write Negative Test</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is initialized and  Cdd_Uart_Write is called with invalid inputs : Source buffer  as NULL PTR</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return E_NOT_OK</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr"/>
-      <c r="T37" s="3" t="inlineStr"/>
-      <c r="U37" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29968</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>UART Write Negative Test</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is initialized and  Cdd_Uart_Write is called with  HW unit ID greater than CDD_UART_MAX_NUM_HWUNIT</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29967</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>UART Write Negative Test</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is uninitialized and  Cdd_Uart_Write is called with valid inputs</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="inlineStr"/>
-      <c r="U39" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29966</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>UART Write Positive Test ISR mode</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is initialized 
-Transmit 20 byte data to remote device  using Cdd_Uart_Write.</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr"/>
-      <c r="T40" s="3" t="inlineStr"/>
-      <c r="U40" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29965</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>UART Write Positive Test : Send data continuously</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is initialized 
-Transmit multiple data with different size in loop to remote device  using Cdd_Uart_Write.</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr"/>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29964</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>UART Write Positive Test Polling mode Large data</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>CDD Uart is initialized 
-Transmit 100 byte data to remote device  using Cdd_Uart_Write.</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -5303,30 +6633,26 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29963</t>
+          <t>MCAL-29982</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>UART Write Positive Test Polling mode</t>
+          <t>Cdd_Uart_CancelWrite Negative Test</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
+      <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -5339,18 +6665,50 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized 
-Transmit 20 byte data to remote device  using Cdd_Uart_Write.</t>
+          <t>CDD Uart is initialized.
+call Cdd_Uart_CancelWrite with invalid HwUnitId</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
+          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -5365,7 +6723,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5380,12 +6738,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -5399,30 +6757,26 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29962</t>
+          <t>MCAL-29985</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>UART Read Negative Test</t>
+          <t>Cdd_Uart_CancelRead Negative Test</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
+      <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -5435,18 +6789,50 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized and Read enable is FALSE.
-Cdd_Uart_Read is called with valid inputs</t>
+          <t>CDD Uart is initialized.
+call Cdd_Uart_CancelRead with invalid HwUnitId</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_VALUE</t>
+          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -5461,7 +6847,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -5476,12 +6862,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -5495,22 +6881,22 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29961</t>
+          <t>MCAL-29989</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>UART Read Negative Test</t>
+          <t>Cdd_Uart_GetWriteStatus Positive Test</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr"/>
@@ -5527,17 +6913,50 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized and  Cdd_Uart_Read is called with invalid inputs : Data count = 0</t>
+          <t>CDD Uart is initialized.
+call Cdd_Uart_GetWriteStatus with valid inputs</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return E_NOT_OK</t>
+          <t>Uart Driver should return E_OK and WriteStatus is updated with the status of write operation</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -5552,7 +6971,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -5567,12 +6986,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -5586,22 +7005,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29960</t>
+          <t>MCAL-29993</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>UART Read Negative Test</t>
+          <t>Cdd_Uart_GetReadStatus Positive Test</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr"/>
@@ -5618,17 +7037,50 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized and  Cdd_Uart_Read is called with invalid inputs : Destination buffer  as NULL PTR</t>
+          <t>CDD Uart is initialized.
+call Cdd_Uart_GetReadStatus with valid inputs</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return E_NOT_OK</t>
+          <t>Uart Driver should return E_OK and ReadStatus is updated with the status of write operation</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -5643,7 +7095,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -5658,12 +7110,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -5677,22 +7129,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29959</t>
+          <t>MCAL-29994</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>UART Read Negative Test</t>
+          <t>Cdd_Uart_GetReadStatus Negative Test</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr"/>
@@ -5709,12 +7161,45 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized and  Cdd_Uart_Read is called with  HW unit ID greater than CDD_UART_MAX_NUM_HWUNIT</t>
+          <t>CDD Uart is initialized.
+call Cdd_Uart_GetReadStatus with invalid HwUnitId</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -5734,7 +7219,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
@@ -5749,12 +7234,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -5768,22 +7253,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29958</t>
+          <t>MCAL-29990</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>UART Read Negative Test</t>
+          <t>Cdd_Uart_GetWriteStatus Negative Test</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr"/>
@@ -5800,17 +7285,50 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is uninitialized and  Cdd_Uart_Read is called with valid inputs</t>
+          <t>CDD Uart is initialized.
+call Cdd_Uart_GetWriteStatus with invalid HwUnitId</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_UNINIT</t>
+          <t>Uart Driver should return CDD_UART_E_PARAM_HWINDEX</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -5825,7 +7343,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -5840,12 +7358,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -5859,22 +7377,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29957</t>
+          <t>MCAL-29995</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>UART Read Positive Test Interrupt Mode</t>
+          <t>Cdd_Uart_GetReadStatus Negative Test</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr"/>
@@ -5891,17 +7409,50 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized in ISR mode and 10 byte data is sent by the remote device  Cdd_Uart_Read is called with valid inputs</t>
+          <t>CDD Uart is initialized.
+call Cdd_Uart_GetReadStatus with ReadStatus as NULL Pointer</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return E_OK &amp; data should be received in the Destination buffer</t>
+          <t>Uart Driver should return CDD_UART_E_PARAM_POINTER</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -5916,7 +7467,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
@@ -5931,12 +7482,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -5950,30 +7501,26 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29956</t>
+          <t>MCAL-29991</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>UART Read Positive Test Polling Mode</t>
+          <t>Cdd_Uart_GetWriteStatus Negative Test</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
+      <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -5986,17 +7533,50 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized in Polling mode and 10 byte data is sent by the remote device  Cdd_Uart_Read is called with valid inputs</t>
+          <t>CDD Uart is initialized.
+call Cdd_Uart_GetWriteStatus with WriteStatus as NULL Pointer</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return E_OK &amp; data should be received in the Destination buffer</t>
+          <t>Uart Driver should return CDD_UART_E_PARAM_POINTER</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -6011,7 +7591,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -6026,12 +7606,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -6045,22 +7625,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29955</t>
+          <t>MCAL-29965</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>UART Deinit Negative Test</t>
+          <t>UART Write Positive Test : Send data continuously</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr"/>
@@ -6072,22 +7652,55 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is uninitialized and Cdd_Uart_Deinit is called</t>
+          <t>CDD Uart is initialized 
+Transmit multiple data with different size in loop to remote device  using Cdd_Uart_Write.</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_NOT_INITIALIZED</t>
+          <t>Uart Driver should return E_OK &amp; data should be transmitted on UART and received on remote device</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -6102,7 +7715,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
@@ -6117,12 +7730,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -6136,22 +7749,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29954</t>
+          <t>MCAL-29998</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>UART Deinit Positive Test</t>
+          <t>CDD UART supports Software Test of Basic Tx RX functionality at 115200 baudrate</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr"/>
@@ -6163,22 +7776,54 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>CDD Uart is initialized and Cdd_Uart_Deinit is called</t>
+          <t>Verify that CDD UART shall be able to transmitted and receive data at 115200 baudrate</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return Cdd_Uart_IsInitialized  as FALSE</t>
+          <t>UART Driver should be able Receive the transmitted data at 115200 baudrate</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -6193,7 +7838,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -6208,12 +7853,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -6227,22 +7872,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32284</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Test Automated</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29953</t>
+          <t>MCAL-29954</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>UART Init Negative Test</t>
+          <t>UART Deinit Positive Test</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr"/>
@@ -6259,17 +7904,49 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>NULL pointer is passed as argument to Cdd_Uart_init and CDD_UART_DEV_ERROR_DETECT is ON &amp; CDD UART is already initialized</t>
+          <t>CDD Uart is initialized and Cdd_Uart_Deinit is called</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Uart_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Uart_Test1/Cdd_Uart_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_ALREADY_INITIALIZED</t>
+          <t>Uart Driver should return Cdd_Uart_IsInitialized  as FALSE</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -6284,7 +7961,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
@@ -6299,12 +7976,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32283</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Automated Tests Run</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -6318,22 +7995,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32348</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Manual Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29952</t>
+          <t>MCAL-30004</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>UART Init Negative Test</t>
+          <t>CDD UART: Cdd_Uart shall verify Configurator support of CDD UART module</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr"/>
@@ -6350,7 +8027,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Not NULL pointer is passed as argument to Cdd_Uart_init and CDD_UART_DEV_ERROR_DETECT is ON</t>
+          <t>Cdd_Uart shall verify Configurator support of CDD UART module by means of a compatible plugin per hardware SoC.</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -6360,7 +8037,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return CDD_UART_E_PARAM_POINTER</t>
+          <t>UART shall be bundled with a compatible loadable plugin across configurator tools such as EB Tresos, DaVinci Configurator.</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -6390,12 +8067,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32347</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Manual Tests Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -6409,30 +8086,26 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32348</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Manual Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29951</t>
+          <t>MCAL-30003</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>UART Init Positive Test</t>
+          <t>CDD UART: MCAL Module State Machine</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
+      <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -6445,7 +8118,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Null pointer is passed as argument to Cdd_Uart_init and CDD_UART_DEV_ERROR_DETECT is OFF</t>
+          <t>CDD UART shall maintain distinct states: Initialized, Un Initialized</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -6455,7 +8128,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return Cdd_Uart_IsInitialized  as TRUE</t>
+          <t>UART must keep a track on internal states, checkable by inspecting UART Driver Status global variable within UART source</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
@@ -6485,12 +8158,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32347</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Manual Tests Run</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -6504,22 +8177,22 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30809</t>
+          <t>MCAL-32348</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Cdd Uart- Manual Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29950</t>
+          <t>MCAL-30002</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>UART Init Positive Test</t>
+          <t>AUTOSAR Configurator (Manual Integration Test Case)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr"/>
@@ -6536,7 +8209,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Null pointer is passed as argument to Cdd_Uart_init and CDD_UART_DEV_ERROR_DETECT is ON</t>
+          <t>The MCAL shall support EB Tresos Configurator for configuration of MCAL modules. The ASIL level is applicable for generated configuration header and source files only.</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6546,7 +8219,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Uart Driver should return Cdd_Uart_IsInitialized  as TRUE</t>
+          <t>The MCAL shall support EB Tresos Configurator for configuration of MCAL modules.</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -6576,12 +8249,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30810</t>
+          <t>MCAL-32347</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00 : CDD_UART - Manual Tests Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -6592,285 +8265,8 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29949</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>GetVersionInfo API Negative Test</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>Null pointer is passed as argument to Cdd_Uart_GetVersionInfo and CDD_UART_GET_VERSION_INFO_API ON, CDD_UART_DEV_ERROR_DETECT is ON</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>Cdd_Uart_GetVersionInfo should return CDD_UART_E_PARAM_POINTER</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N57" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q57" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R57" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S57" s="3" t="inlineStr"/>
-      <c r="T57" s="3" t="inlineStr"/>
-      <c r="U57" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29948</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>GetVersionInfo API Positive Test</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>No Associated Issues provided for the Test Case in Jira.</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>Valid versioninfo pointer is passed as argument to Cdd_Uart_GetVersionInfo and CDD_UART_GET_VERSION_INFO_API ON, CDD_UART_DEV_ERROR_DETECT is OFF</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>Cdd_Uart_GetVersionInfo should return the vendor ID, module ID, software major version, software minor version and software patch version</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q58" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R58" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S58" s="3" t="inlineStr"/>
-      <c r="T58" s="3" t="inlineStr"/>
-      <c r="U58" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30809</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Cdd Uart- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29947</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>GetVersionInfo API Positive Test</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>Valid versioninfo pointer is passed as argument to Cdd_Uart_GetVersionInfo and CDD_UART_GET_VERSION_INFO_API ON, CDD_UART_DEV_ERROR_DETECT is ON</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>Cdd_Uart_GetVersionInfo should return the vendor ID, module ID, software major version, software minor version and software patch version</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N59" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="inlineStr">
-        <is>
-          <t>CDD UART</t>
-        </is>
-      </c>
-      <c r="Q59" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30810</t>
-        </is>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD_UART - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S59" s="3" t="inlineStr"/>
-      <c r="T59" s="3" t="inlineStr"/>
-      <c r="U59" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:U59"/>
+  <autoFilter ref="A1:U56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
